--- a/competition/專題競賽資訊.xlsx
+++ b/competition/專題競賽資訊.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ntubedutw-my.sharepoint.com/personal/11246065_ntub_edu_tw/Documents/115畢業專題文件/E 競賽報名文件/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yxuan/Documents/SaveMyBook/competition/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="13_ncr:1_{F59CF4A7-E1C1-4005-8231-18283ADEE2ED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{99832A3A-3156-4C72-9317-2951B99DEBE0}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E97525BA-6511-D841-AC77-47B43E930B86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{285F9FD4-B296-469E-ADA7-FB304A9A05A2}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="28340" windowHeight="18460" activeTab="1" xr2:uid="{285F9FD4-B296-469E-ADA7-FB304A9A05A2}"/>
   </bookViews>
   <sheets>
     <sheet name="2025年相關競賽" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="156">
   <si>
     <t>競賽名稱</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -516,9 +516,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>2025全國AI專題創意競賽</t>
-  </si>
-  <si>
     <t>2025/9/8(一)~2025/11/26(三)</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -624,9 +621,6 @@
     <t>萬潤2025創新創意競賽</t>
   </si>
   <si>
-    <t>~2026/8/31(一)</t>
-  </si>
-  <si>
     <t>初賽：2026/9/1(二)~2025/9/11(五)
 決賽：2026/10/22(四)</t>
   </si>
@@ -655,6 +649,63 @@
   </si>
   <si>
     <t>萬潤2026創新創意競賽</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2025全國AI專題創意競賽</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026全國AI專題創意競賽</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026/9/1(二)~2026/12/1(二)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>初賽：2026/12/11(五)
+決賽：2026/12/19(六)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>初賽：書面審查
+決賽：國立臺南大學中山館</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>國立臺南大學</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://bhuntr.com/tw/competitions/jnlxrqcq6vyvmq6t7t</t>
+  </si>
+  <si>
+    <t>2026 全國大專院校產學創新實作競賽</t>
+  </si>
+  <si>
+    <t>https://eedept.ncue.edu.tw/innovation2026/index.html</t>
+  </si>
+  <si>
+    <t>初賽：2026/11/12(四)
+決賽：2026/11/19(四)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>初賽：書面審查
+決賽：國立彰化師大工學院</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>國立彰化師範大學工學院、彰化縣產學精進協會</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>~2026/8/31(一)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>~2026/10/22(四）</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -662,7 +713,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="8">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -766,7 +817,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -810,6 +861,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1057,19 +1111,19 @@
     <tabColor theme="4" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:G23"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="3.5546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="57.6640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.44140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="45.5546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="123.6640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="6"/>
+    <col min="1" max="1" width="3.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="57.7109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.42578125" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.28515625" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.28515625" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="45.5703125" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="123.7109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.85546875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="1" customFormat="1">
       <c r="A1" s="2" t="s">
         <v>69</v>
       </c>
@@ -1092,7 +1146,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="38">
       <c r="A2" s="5">
         <v>1</v>
       </c>
@@ -1115,7 +1169,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="38">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -1138,30 +1192,30 @@
         <v>86</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="38">
       <c r="A4" s="5">
         <v>3</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="D4" s="7" t="s">
         <v>128</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="E4" s="7" t="s">
         <v>129</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="F4" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="F4" s="9" t="s">
+      <c r="G4" s="8" t="s">
         <v>131</v>
       </c>
-      <c r="G4" s="8" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:7">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -1184,7 +1238,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="38">
       <c r="A6" s="5">
         <v>5</v>
       </c>
@@ -1207,12 +1261,12 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="38">
       <c r="A7" s="5">
         <v>6</v>
       </c>
       <c r="B7" s="14" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C7" s="6" t="s">
         <v>63</v>
@@ -1230,7 +1284,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="8" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="38">
       <c r="A8" s="5">
         <v>7</v>
       </c>
@@ -1253,12 +1307,12 @@
         <v>76</v>
       </c>
     </row>
-    <row r="9" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="38">
       <c r="A9" s="5">
         <v>8</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="C9" s="6" t="s">
         <v>53</v>
@@ -1276,30 +1330,30 @@
         <v>56</v>
       </c>
     </row>
-    <row r="10" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="57">
       <c r="A10" s="5">
         <v>9</v>
       </c>
       <c r="B10" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="C10" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="D10" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="E10" s="7" t="s">
         <v>122</v>
       </c>
-      <c r="E10" s="7" t="s">
+      <c r="F10" s="11" t="s">
         <v>123</v>
       </c>
-      <c r="F10" s="11" t="s">
+      <c r="G10" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="G10" s="8" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:7" ht="38">
       <c r="A11" s="5">
         <v>10</v>
       </c>
@@ -1322,7 +1376,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="38">
       <c r="A12" s="5">
         <v>11</v>
       </c>
@@ -1345,7 +1399,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="38">
       <c r="A13" s="5">
         <v>12</v>
       </c>
@@ -1368,7 +1422,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="38">
       <c r="A14" s="5">
         <v>13</v>
       </c>
@@ -1391,7 +1445,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="38">
       <c r="A15" s="5">
         <v>14</v>
       </c>
@@ -1414,7 +1468,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="16" spans="1:7" ht="47.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="57">
       <c r="A16" s="5">
         <v>15</v>
       </c>
@@ -1437,7 +1491,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="17" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="38">
       <c r="A17" s="5">
         <v>16</v>
       </c>
@@ -1460,7 +1514,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="18" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" ht="38">
       <c r="A18" s="5">
         <v>17</v>
       </c>
@@ -1483,7 +1537,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="19" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="38">
       <c r="A19" s="5">
         <v>18</v>
       </c>
@@ -1506,7 +1560,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" ht="19">
       <c r="A20" s="5">
         <v>19</v>
       </c>
@@ -1529,30 +1583,30 @@
         <v>107</v>
       </c>
     </row>
-    <row r="21" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="38">
       <c r="A21" s="5">
         <v>20</v>
       </c>
       <c r="B21" s="14" t="s">
+        <v>142</v>
+      </c>
+      <c r="C21" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="C21" s="6" t="s">
+      <c r="D21" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="D21" s="7" t="s">
+      <c r="E21" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="F21" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="G21" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="F21" s="7" t="s">
-        <v>111</v>
-      </c>
-      <c r="G21" s="8" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:7">
       <c r="A22" s="5">
         <v>21</v>
       </c>
@@ -1575,27 +1629,27 @@
         <v>95</v>
       </c>
     </row>
-    <row r="23" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="38">
       <c r="A23" s="5">
         <v>22</v>
       </c>
       <c r="B23" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="C23" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="C23" s="6" t="s">
+      <c r="D23" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="E23" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="E23" s="7" t="s">
+      <c r="F23" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="F23" s="6" t="s">
+      <c r="G23" s="8" t="s">
         <v>118</v>
-      </c>
-      <c r="G23" s="8" t="s">
-        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -1634,19 +1688,19 @@
     <tabColor theme="4"/>
   </sheetPr>
   <dimension ref="A1:G22"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="2.88671875" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="36.88671875" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="24.109375" style="6" customWidth="1"/>
-    <col min="4" max="4" width="33.33203125" style="6" customWidth="1"/>
-    <col min="5" max="5" width="19.21875" style="6" customWidth="1"/>
-    <col min="6" max="6" width="43.88671875" style="6" customWidth="1"/>
-    <col min="7" max="7" width="42.77734375" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="6"/>
+    <col min="1" max="1" width="3.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="36.85546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="24.140625" style="6" customWidth="1"/>
+    <col min="4" max="4" width="33.28515625" style="6" customWidth="1"/>
+    <col min="5" max="5" width="22.7109375" style="6" customWidth="1"/>
+    <col min="6" max="6" width="43.85546875" style="6" customWidth="1"/>
+    <col min="7" max="7" width="42.7109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.85546875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="1" customFormat="1">
       <c r="A1" s="2" t="s">
         <v>69</v>
       </c>
@@ -1669,44 +1723,44 @@
         <v>88</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="38">
       <c r="A2" s="5">
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>134</v>
+        <v>154</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>64</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" ht="31.5" x14ac:dyDescent="0.25">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" ht="38">
       <c r="A3" s="5">
         <v>2</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="E3" s="7" t="s">
         <v>139</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>141</v>
       </c>
       <c r="F3" s="11" t="s">
         <v>87</v>
@@ -1715,23 +1769,53 @@
         <v>56</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="38">
       <c r="A4" s="5">
         <v>3</v>
       </c>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="8"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B4" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="F4" s="11" t="s">
+        <v>147</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" ht="38">
       <c r="A5" s="5">
         <v>4</v>
       </c>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="G5" s="8"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B5" s="6" t="s">
+        <v>149</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>155</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="F5" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="A6" s="5">
         <v>5</v>
       </c>
@@ -1740,7 +1824,7 @@
       <c r="F6" s="3"/>
       <c r="G6" s="8"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7">
       <c r="A7" s="5">
         <v>6</v>
       </c>
@@ -1749,7 +1833,7 @@
       <c r="F7" s="4"/>
       <c r="G7" s="8"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="15.75">
       <c r="A8" s="5">
         <v>7</v>
       </c>
@@ -1758,7 +1842,7 @@
       <c r="F8" s="11"/>
       <c r="G8" s="8"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="15.75">
       <c r="A9" s="5">
         <v>8</v>
       </c>
@@ -1767,7 +1851,7 @@
       <c r="F9" s="11"/>
       <c r="G9" s="8"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="15.75">
       <c r="A10" s="5">
         <v>9</v>
       </c>
@@ -1775,7 +1859,7 @@
       <c r="E10" s="7"/>
       <c r="G10" s="8"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="15.75">
       <c r="A11" s="5">
         <v>10</v>
       </c>
@@ -1784,59 +1868,59 @@
       <c r="F11" s="3"/>
       <c r="G11" s="8"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="15.75">
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
       <c r="G12" s="8"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="15.75">
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
       <c r="G13" s="8"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="15.75">
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
       <c r="F14" s="3"/>
       <c r="G14" s="8"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="15.75">
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
       <c r="F15" s="12"/>
       <c r="G15" s="8"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="15.75">
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
       <c r="F16" s="3"/>
       <c r="G16" s="8"/>
     </row>
-    <row r="17" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="4:7" ht="15.75">
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
       <c r="G17" s="8"/>
     </row>
-    <row r="18" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="4:7" ht="15.75">
       <c r="D18" s="7"/>
       <c r="E18" s="7"/>
       <c r="G18" s="8"/>
     </row>
-    <row r="19" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="4:7" ht="15.75">
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
       <c r="G19" s="8"/>
     </row>
-    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="4:7" ht="15.75">
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
       <c r="G20" s="8"/>
     </row>
-    <row r="21" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="4:7" ht="15.75">
       <c r="G21" s="8"/>
     </row>
-    <row r="22" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="4:7" ht="15.75">
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
       <c r="G22" s="8"/>
@@ -1858,19 +1942,19 @@
     <tabColor theme="4"/>
   </sheetPr>
   <dimension ref="A1:G22"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.85546875" defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="3.5546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="57.6640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.44140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="35.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="22.33203125" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="45.5546875" style="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="123.6640625" style="6" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="8.88671875" style="6"/>
+    <col min="1" max="1" width="3.5703125" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="57.7109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="28.42578125" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="35.28515625" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="22.28515625" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="45.5703125" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="123.7109375" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.85546875" style="6"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="1" customFormat="1" ht="16.5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" s="1" customFormat="1">
       <c r="A1" s="2" t="s">
         <v>69</v>
       </c>
@@ -1893,12 +1977,12 @@
         <v>88</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7">
       <c r="A2" s="5">
         <v>1</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D2" s="7"/>
       <c r="E2" s="7"/>
@@ -1907,7 +1991,7 @@
       </c>
       <c r="G2" s="8"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="15.75">
       <c r="A3" s="5">
         <v>2</v>
       </c>
@@ -1916,7 +2000,7 @@
       <c r="F3" s="9"/>
       <c r="G3" s="8"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="15.75">
       <c r="A4" s="5">
         <v>3</v>
       </c>
@@ -1924,7 +2008,7 @@
       <c r="F4" s="10"/>
       <c r="G4" s="8"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" ht="15.75">
       <c r="A5" s="5">
         <v>4</v>
       </c>
@@ -1932,7 +2016,7 @@
       <c r="E5" s="7"/>
       <c r="G5" s="8"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" ht="15.75">
       <c r="A6" s="5">
         <v>5</v>
       </c>
@@ -1941,7 +2025,7 @@
       <c r="F6" s="3"/>
       <c r="G6" s="8"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="15.75">
       <c r="A7" s="5">
         <v>6</v>
       </c>
@@ -1950,7 +2034,7 @@
       <c r="F7" s="4"/>
       <c r="G7" s="8"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" ht="15.75">
       <c r="A8" s="5">
         <v>7</v>
       </c>
@@ -1959,7 +2043,7 @@
       <c r="F8" s="11"/>
       <c r="G8" s="8"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" ht="15.75">
       <c r="A9" s="5">
         <v>8</v>
       </c>
@@ -1968,7 +2052,7 @@
       <c r="F9" s="11"/>
       <c r="G9" s="8"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" ht="15.75">
       <c r="A10" s="5">
         <v>9</v>
       </c>
@@ -1976,7 +2060,7 @@
       <c r="E10" s="7"/>
       <c r="G10" s="8"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" ht="15.75">
       <c r="A11" s="5">
         <v>10</v>
       </c>
@@ -1985,59 +2069,59 @@
       <c r="F11" s="3"/>
       <c r="G11" s="8"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" ht="15.75">
       <c r="D12" s="7"/>
       <c r="E12" s="7"/>
       <c r="G12" s="8"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" ht="15.75">
       <c r="D13" s="7"/>
       <c r="E13" s="7"/>
       <c r="G13" s="8"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="15.75">
       <c r="D14" s="7"/>
       <c r="E14" s="7"/>
       <c r="F14" s="3"/>
       <c r="G14" s="8"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7" ht="15.75">
       <c r="D15" s="7"/>
       <c r="E15" s="7"/>
       <c r="F15" s="12"/>
       <c r="G15" s="8"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="15.75">
       <c r="D16" s="7"/>
       <c r="E16" s="7"/>
       <c r="F16" s="3"/>
       <c r="G16" s="8"/>
     </row>
-    <row r="17" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="4:7" ht="15.75">
       <c r="D17" s="7"/>
       <c r="E17" s="7"/>
       <c r="G17" s="8"/>
     </row>
-    <row r="18" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="4:7" ht="15.75">
       <c r="D18" s="7"/>
       <c r="E18" s="7"/>
       <c r="G18" s="8"/>
     </row>
-    <row r="19" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="4:7" ht="15.75">
       <c r="D19" s="7"/>
       <c r="E19" s="7"/>
       <c r="G19" s="8"/>
     </row>
-    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="4:7" ht="15.75">
       <c r="D20" s="7"/>
       <c r="E20" s="7"/>
       <c r="F20" s="7"/>
       <c r="G20" s="8"/>
     </row>
-    <row r="21" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="4:7" ht="15.75">
       <c r="G21" s="8"/>
     </row>
-    <row r="22" spans="4:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="4:7" ht="15.75">
       <c r="D22" s="7"/>
       <c r="E22" s="7"/>
       <c r="G22" s="8"/>
